--- a/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · Valor, agravio y mujer</t>
   </si>
   <si>
-    <t>Para María Isabel Cuena · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para María Isabel Cuena · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>
@@ -123,7 +123,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 227 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 227 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t/>
@@ -138,7 +138,7 @@
     <t>928–1182</t>
   </si>
   <si>
-    <t>Tiene 255 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 255 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|c789a3f8-e1d4-478c-ba08-4dbd76e91585</t>
@@ -150,7 +150,7 @@
     <t>Décima · Espinela</t>
   </si>
   <si>
-    <t>Sus 35 versos no encajan con «Espinela», que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30).</t>
+    <t>Sus 35 versos no encajan en una décima espinela, que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30).</t>
   </si>
   <si>
     <t>L|fddd8345-3919-4484-b699-b24b81040928</t>
@@ -159,7 +159,7 @@
     <t>1839–2003</t>
   </si>
   <si>
-    <t>Tiene 165 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 165 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|e8921ca3-f11c-412e-b64e-a58234282eb1</t>
@@ -1560,7 +1560,7 @@
 patron_alternativo (354–355)</t>
   </si>
   <si>
-    <t>Revisar: Tiene 227 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Tiene 227 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>redondilla</t>
@@ -1632,7 +1632,7 @@
 hipometrico (1172–1172)</t>
   </si>
   <si>
-    <t>Revisar: Tiene 255 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Tiene 255 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>1183–1262</t>
@@ -1658,7 +1658,7 @@
 rima_defectuosa (1276–1291)</t>
   </si>
   <si>
-    <t>Revisar: Sus 35 versos no encajan con «Espinela», que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30).</t>
+    <t>Revisar: Sus 35 versos no encajan en una décima espinela, que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30).</t>
   </si>
   <si>
     <t xml:space="preserve">hipometrico (1307–1307)
@@ -1743,7 +1743,7 @@
 hipermetrico (2001–2001)</t>
   </si>
   <si>
-    <t>Revisar: Tiene 165 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Tiene 165 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t xml:space="preserve">hipermetrico (2016–2016)

--- a/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -399,10 +399,10 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
-  </si>
-  <si>
-    <t>Informativa</t>
+    <t>Sílabas del verso</t>
+  </si>
+  <si>
+    <t>Revisar</t>
   </si>
   <si>
     <t>22</t>
@@ -3247,7 +3247,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -8407,17 +8407,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H15">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H10:H161">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H35:H36">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H54">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H57">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H161">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="554">
   <si>
     <t>Migración métrica · Valor, agravio y mujer</t>
   </si>
   <si>
-    <t>Para María Isabel Cuena · generado el 2026-09-20</t>
+    <t>Para María Isabel Cuena · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -123,7 +123,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 227 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 227 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t/>
@@ -138,7 +138,7 @@
     <t>928–1182</t>
   </si>
   <si>
-    <t>Tiene 255 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 255 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t>L|c789a3f8-e1d4-478c-ba08-4dbd76e91585</t>
@@ -150,7 +150,7 @@
     <t>Décima · Espinela</t>
   </si>
   <si>
-    <t>Sus 35 versos no encajan en una décima espinela, que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30).</t>
+    <t>Sus 35 versos no encajan en una décima espinela, que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t>L|fddd8345-3919-4484-b699-b24b81040928</t>
@@ -159,7 +159,7 @@
     <t>1839–2003</t>
   </si>
   <si>
-    <t>Tiene 165 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 165 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t>L|e8921ca3-f11c-412e-b64e-a58234282eb1</t>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t>Décima · Espinela (1267–1301)</t>
+  </si>
+  <si>
+    <t>Pasa a ser una desviación de rima</t>
   </si>
   <si>
     <t>D|f8ef7c05-1f1c-411c-b9ac-4b9cc3db44ac</t>
@@ -4966,7 +4969,7 @@
         <v>36</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>36</v>
@@ -4978,7 +4981,7 @@
         <v>36</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4998,7 +5001,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>36</v>
@@ -5010,7 +5013,7 @@
         <v>36</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5018,10 +5021,10 @@
         <v>135</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>144</v>
@@ -5042,7 +5045,7 @@
         <v>36</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5050,16 +5053,16 @@
         <v>168</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>170</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>133</v>
@@ -5074,7 +5077,7 @@
         <v>36</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5082,10 +5085,10 @@
         <v>135</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>137</v>
@@ -5106,7 +5109,7 @@
         <v>36</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5114,10 +5117,10 @@
         <v>135</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>144</v>
@@ -5138,7 +5141,7 @@
         <v>36</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5146,10 +5149,10 @@
         <v>135</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>144</v>
@@ -5170,7 +5173,7 @@
         <v>36</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5178,10 +5181,10 @@
         <v>135</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>137</v>
@@ -5202,7 +5205,7 @@
         <v>36</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5210,10 +5213,10 @@
         <v>135</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>137</v>
@@ -5234,7 +5237,7 @@
         <v>36</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5242,10 +5245,10 @@
         <v>135</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>144</v>
@@ -5266,7 +5269,7 @@
         <v>36</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5274,10 +5277,10 @@
         <v>135</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>137</v>
@@ -5298,7 +5301,7 @@
         <v>36</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5306,16 +5309,16 @@
         <v>128</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>131</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>133</v>
@@ -5330,7 +5333,7 @@
         <v>36</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5338,10 +5341,10 @@
         <v>135</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>137</v>
@@ -5362,7 +5365,7 @@
         <v>36</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5370,10 +5373,10 @@
         <v>135</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>137</v>
@@ -5394,7 +5397,7 @@
         <v>36</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5402,10 +5405,10 @@
         <v>135</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>144</v>
@@ -5426,7 +5429,7 @@
         <v>36</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5434,16 +5437,16 @@
         <v>128</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>131</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>133</v>
@@ -5458,7 +5461,7 @@
         <v>36</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5466,10 +5469,10 @@
         <v>135</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>137</v>
@@ -5490,7 +5493,7 @@
         <v>36</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5498,10 +5501,10 @@
         <v>135</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>144</v>
@@ -5522,7 +5525,7 @@
         <v>36</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5530,10 +5533,10 @@
         <v>135</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>137</v>
@@ -5554,7 +5557,7 @@
         <v>36</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5562,10 +5565,10 @@
         <v>135</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>137</v>
@@ -5586,7 +5589,7 @@
         <v>36</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5594,10 +5597,10 @@
         <v>135</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>137</v>
@@ -5618,7 +5621,7 @@
         <v>36</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5626,10 +5629,10 @@
         <v>135</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>137</v>
@@ -5650,7 +5653,7 @@
         <v>36</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5658,10 +5661,10 @@
         <v>135</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>137</v>
@@ -5682,7 +5685,7 @@
         <v>36</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="77" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5690,10 +5693,10 @@
         <v>135</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>137</v>
@@ -5714,7 +5717,7 @@
         <v>36</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5722,10 +5725,10 @@
         <v>135</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>137</v>
@@ -5746,7 +5749,7 @@
         <v>36</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5754,10 +5757,10 @@
         <v>135</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>144</v>
@@ -5778,7 +5781,7 @@
         <v>36</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="80" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5786,10 +5789,10 @@
         <v>135</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>137</v>
@@ -5810,7 +5813,7 @@
         <v>36</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5818,10 +5821,10 @@
         <v>135</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>137</v>
@@ -5842,7 +5845,7 @@
         <v>36</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5850,10 +5853,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>137</v>
@@ -5874,7 +5877,7 @@
         <v>36</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5882,10 +5885,10 @@
         <v>135</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>137</v>
@@ -5906,7 +5909,7 @@
         <v>36</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="84" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5914,10 +5917,10 @@
         <v>135</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>137</v>
@@ -5938,7 +5941,7 @@
         <v>36</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5946,16 +5949,16 @@
         <v>128</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>131</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>133</v>
@@ -5970,7 +5973,7 @@
         <v>36</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5978,10 +5981,10 @@
         <v>135</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>137</v>
@@ -6002,7 +6005,7 @@
         <v>36</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6010,10 +6013,10 @@
         <v>135</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>137</v>
@@ -6034,7 +6037,7 @@
         <v>36</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6042,16 +6045,16 @@
         <v>135</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>144</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>145</v>
@@ -6066,7 +6069,7 @@
         <v>36</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="89" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6074,10 +6077,10 @@
         <v>135</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>137</v>
@@ -6098,7 +6101,7 @@
         <v>36</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6106,10 +6109,10 @@
         <v>135</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>137</v>
@@ -6130,7 +6133,7 @@
         <v>36</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6138,10 +6141,10 @@
         <v>135</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>144</v>
@@ -6162,7 +6165,7 @@
         <v>36</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6170,16 +6173,16 @@
         <v>135</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>144</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>145</v>
@@ -6194,7 +6197,7 @@
         <v>36</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6202,10 +6205,10 @@
         <v>135</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>137</v>
@@ -6226,7 +6229,7 @@
         <v>36</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6234,10 +6237,10 @@
         <v>135</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>137</v>
@@ -6258,7 +6261,7 @@
         <v>36</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6266,10 +6269,10 @@
         <v>135</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>144</v>
@@ -6290,7 +6293,7 @@
         <v>36</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6298,10 +6301,10 @@
         <v>135</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>137</v>
@@ -6322,7 +6325,7 @@
         <v>36</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6330,10 +6333,10 @@
         <v>135</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>144</v>
@@ -6354,7 +6357,7 @@
         <v>36</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6362,10 +6365,10 @@
         <v>135</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>137</v>
@@ -6386,7 +6389,7 @@
         <v>36</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6394,10 +6397,10 @@
         <v>135</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>137</v>
@@ -6418,7 +6421,7 @@
         <v>36</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="100" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6426,10 +6429,10 @@
         <v>135</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>137</v>
@@ -6450,7 +6453,7 @@
         <v>36</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6458,10 +6461,10 @@
         <v>135</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>137</v>
@@ -6482,7 +6485,7 @@
         <v>36</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6490,10 +6493,10 @@
         <v>135</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>137</v>
@@ -6514,7 +6517,7 @@
         <v>36</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="103" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6522,10 +6525,10 @@
         <v>135</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>144</v>
@@ -6546,7 +6549,7 @@
         <v>36</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="104" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6554,10 +6557,10 @@
         <v>135</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>144</v>
@@ -6578,7 +6581,7 @@
         <v>36</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="105" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6586,10 +6589,10 @@
         <v>135</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>137</v>
@@ -6610,7 +6613,7 @@
         <v>36</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6618,16 +6621,16 @@
         <v>135</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>144</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>145</v>
@@ -6642,7 +6645,7 @@
         <v>36</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="107" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6650,10 +6653,10 @@
         <v>135</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>137</v>
@@ -6674,7 +6677,7 @@
         <v>36</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6682,10 +6685,10 @@
         <v>135</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>144</v>
@@ -6706,7 +6709,7 @@
         <v>36</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6714,10 +6717,10 @@
         <v>135</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>144</v>
@@ -6738,7 +6741,7 @@
         <v>36</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="110" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6746,10 +6749,10 @@
         <v>135</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>137</v>
@@ -6770,7 +6773,7 @@
         <v>36</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="111" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6778,10 +6781,10 @@
         <v>135</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>137</v>
@@ -6802,7 +6805,7 @@
         <v>36</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="112" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6810,10 +6813,10 @@
         <v>135</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>144</v>
@@ -6834,7 +6837,7 @@
         <v>36</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="113" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6842,10 +6845,10 @@
         <v>135</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>137</v>
@@ -6866,7 +6869,7 @@
         <v>36</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="114" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6874,10 +6877,10 @@
         <v>135</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>137</v>
@@ -6898,7 +6901,7 @@
         <v>36</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6906,10 +6909,10 @@
         <v>135</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>137</v>
@@ -6930,7 +6933,7 @@
         <v>36</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6938,10 +6941,10 @@
         <v>135</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>137</v>
@@ -6962,7 +6965,7 @@
         <v>36</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="117" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6970,10 +6973,10 @@
         <v>135</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>137</v>
@@ -6994,7 +6997,7 @@
         <v>36</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7002,10 +7005,10 @@
         <v>135</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>144</v>
@@ -7026,7 +7029,7 @@
         <v>36</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="119" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7034,10 +7037,10 @@
         <v>135</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>137</v>
@@ -7058,7 +7061,7 @@
         <v>36</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="120" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7066,10 +7069,10 @@
         <v>135</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>137</v>
@@ -7090,7 +7093,7 @@
         <v>36</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="121" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7098,10 +7101,10 @@
         <v>135</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>137</v>
@@ -7122,7 +7125,7 @@
         <v>36</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="122" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7130,10 +7133,10 @@
         <v>135</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>137</v>
@@ -7154,7 +7157,7 @@
         <v>36</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7162,10 +7165,10 @@
         <v>135</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>144</v>
@@ -7186,7 +7189,7 @@
         <v>36</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="124" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7194,10 +7197,10 @@
         <v>135</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>137</v>
@@ -7218,7 +7221,7 @@
         <v>36</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7226,10 +7229,10 @@
         <v>135</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>137</v>
@@ -7250,7 +7253,7 @@
         <v>36</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="126" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7258,16 +7261,16 @@
         <v>135</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>144</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>145</v>
@@ -7282,7 +7285,7 @@
         <v>36</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="127" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7290,10 +7293,10 @@
         <v>135</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>144</v>
@@ -7314,7 +7317,7 @@
         <v>36</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="128" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7322,10 +7325,10 @@
         <v>135</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>144</v>
@@ -7346,7 +7349,7 @@
         <v>36</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="129" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7354,10 +7357,10 @@
         <v>135</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>137</v>
@@ -7378,7 +7381,7 @@
         <v>36</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="130" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7386,10 +7389,10 @@
         <v>135</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>137</v>
@@ -7410,7 +7413,7 @@
         <v>36</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="131" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7418,10 +7421,10 @@
         <v>135</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>137</v>
@@ -7442,7 +7445,7 @@
         <v>36</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="132" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7450,10 +7453,10 @@
         <v>135</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>137</v>
@@ -7474,7 +7477,7 @@
         <v>36</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="133" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7482,10 +7485,10 @@
         <v>135</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>137</v>
@@ -7506,7 +7509,7 @@
         <v>36</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="134" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7514,10 +7517,10 @@
         <v>135</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>144</v>
@@ -7538,7 +7541,7 @@
         <v>36</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="135" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7546,10 +7549,10 @@
         <v>135</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>137</v>
@@ -7570,7 +7573,7 @@
         <v>36</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="136" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7578,10 +7581,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>144</v>
@@ -7602,7 +7605,7 @@
         <v>36</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7610,10 +7613,10 @@
         <v>135</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>137</v>
@@ -7634,7 +7637,7 @@
         <v>36</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="138" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7642,10 +7645,10 @@
         <v>135</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>144</v>
@@ -7666,7 +7669,7 @@
         <v>36</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7674,10 +7677,10 @@
         <v>135</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>137</v>
@@ -7698,7 +7701,7 @@
         <v>36</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="140" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7706,10 +7709,10 @@
         <v>135</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>144</v>
@@ -7730,7 +7733,7 @@
         <v>36</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="141" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7738,10 +7741,10 @@
         <v>135</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>137</v>
@@ -7762,7 +7765,7 @@
         <v>36</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="142" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7770,10 +7773,10 @@
         <v>135</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>137</v>
@@ -7794,7 +7797,7 @@
         <v>36</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="143" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7802,10 +7805,10 @@
         <v>135</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>137</v>
@@ -7826,7 +7829,7 @@
         <v>36</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="144" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7834,10 +7837,10 @@
         <v>135</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>137</v>
@@ -7858,7 +7861,7 @@
         <v>36</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="145" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7866,10 +7869,10 @@
         <v>135</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>137</v>
@@ -7890,7 +7893,7 @@
         <v>36</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="146" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7898,10 +7901,10 @@
         <v>135</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>144</v>
@@ -7922,7 +7925,7 @@
         <v>36</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="147" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7930,10 +7933,10 @@
         <v>135</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>137</v>
@@ -7954,7 +7957,7 @@
         <v>36</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="148" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7962,10 +7965,10 @@
         <v>135</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>144</v>
@@ -7986,7 +7989,7 @@
         <v>36</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="149" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7994,10 +7997,10 @@
         <v>135</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>137</v>
@@ -8018,7 +8021,7 @@
         <v>36</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="150" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8026,10 +8029,10 @@
         <v>135</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>137</v>
@@ -8050,7 +8053,7 @@
         <v>36</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="151" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8058,10 +8061,10 @@
         <v>135</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>137</v>
@@ -8082,7 +8085,7 @@
         <v>36</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="152" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8090,10 +8093,10 @@
         <v>135</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>137</v>
@@ -8114,7 +8117,7 @@
         <v>36</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="153" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8122,10 +8125,10 @@
         <v>135</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>137</v>
@@ -8146,7 +8149,7 @@
         <v>36</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="154" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8154,10 +8157,10 @@
         <v>135</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>137</v>
@@ -8178,7 +8181,7 @@
         <v>36</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="155" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8186,10 +8189,10 @@
         <v>135</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>137</v>
@@ -8210,7 +8213,7 @@
         <v>36</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="156" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8218,10 +8221,10 @@
         <v>135</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>137</v>
@@ -8242,7 +8245,7 @@
         <v>36</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8250,10 +8253,10 @@
         <v>135</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>137</v>
@@ -8274,7 +8277,7 @@
         <v>36</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="158" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8282,10 +8285,10 @@
         <v>135</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>137</v>
@@ -8306,7 +8309,7 @@
         <v>36</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="159" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8314,10 +8317,10 @@
         <v>135</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>137</v>
@@ -8338,7 +8341,7 @@
         <v>36</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="160" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8346,10 +8349,10 @@
         <v>135</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>137</v>
@@ -8370,7 +8373,7 @@
         <v>36</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="161" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8378,10 +8381,10 @@
         <v>135</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>137</v>
@@ -8402,7 +8405,7 @@
         <v>36</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -8440,13 +8443,13 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>72</v>
@@ -8455,22 +8458,22 @@
         <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>26</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8487,25 +8490,25 @@
         <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8522,25 +8525,25 @@
         <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8554,28 +8557,28 @@
         <v>192</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8592,25 +8595,25 @@
         <v>87</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8624,28 +8627,28 @@
         <v>92</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8662,25 +8665,25 @@
         <v>91</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8694,28 +8697,28 @@
         <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8732,25 +8735,25 @@
         <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8758,34 +8761,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C10" s="3">
         <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8799,28 +8802,28 @@
         <v>4</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8834,28 +8837,28 @@
         <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8872,25 +8875,25 @@
         <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8907,25 +8910,25 @@
         <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8933,34 +8936,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C15" s="3">
         <v>20</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -8977,25 +8980,25 @@
         <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9003,34 +9006,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C17" s="3">
         <v>20</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9047,25 +9050,25 @@
         <v>104</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9073,34 +9076,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C19" s="3">
         <v>20</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9117,25 +9120,25 @@
         <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9143,34 +9146,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C21" s="3">
         <v>20</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9187,25 +9190,25 @@
         <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9222,25 +9225,25 @@
         <v>98</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9254,28 +9257,28 @@
         <v>72</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9292,25 +9295,25 @@
         <v>117</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9324,28 +9327,28 @@
         <v>120</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9362,25 +9365,25 @@
         <v>121</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
@@ -123,7 +123,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 227 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 227 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t/>
@@ -138,7 +138,7 @@
     <t>928–1182</t>
   </si>
   <si>
-    <t>Tiene 255 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 255 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|c789a3f8-e1d4-478c-ba08-4dbd76e91585</t>
@@ -150,7 +150,7 @@
     <t>Décima · Espinela</t>
   </si>
   <si>
-    <t>Sus 35 versos no encajan en una décima espinela, que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Sus 35 versos no encajan en una décima espinela, que se compone de unidades completas de 10 versos. Encajaría con 5 versos más (40) o con 5 versos menos (30).</t>
   </si>
   <si>
     <t>L|fddd8345-3919-4484-b699-b24b81040928</t>
@@ -159,7 +159,7 @@
     <t>1839–2003</t>
   </si>
   <si>
-    <t>Tiene 165 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 165 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|e8921ca3-f11c-412e-b64e-a58234282eb1</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -177,7 +177,7 @@
     <t>Esquema de rima · 48 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
   </si>
   <si>
     <t>R|84aeb246-a32c-4f50-b6bf-bfca03817a21|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/valor-agravio-y-mujer.xlsx
@@ -669,7 +669,7 @@
     <t>mayoria_agudas</t>
   </si>
   <si>
-    <t>En un romance con asonancia en «a» el final agudo ya va implícito, así que no se registra aparte</t>
+    <t>La asonancia de este romance es en «a», así que el final agudo ya va implícito: no se registra aparte</t>
   </si>
   <si>
     <t>D|dc10e969-061f-462b-b425-f26372d315cb</t>
